--- a/human_validation/judge/kor/judge_D002_S004_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S004_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -559,12 +556,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 평소에 잘 챙기던 사소한 일들을 자꾸 잊어버려서 오게 됐어요. 예를 들면 전화 회신을 깜빡하거나, 등록 서류 제출을 놓치거나, 퇴근길에 들르려고 했던 심부름을 완전히 잊어버리는 식으로요. 이런 일이 꽤 자주 생겨서 도움을 받아야겠다고 생각했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 기억력 문제를 언제 처음 알아차리셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 저녁 자격증 과정을 시작했던 15개월 전쯤부터 관리하기가 힘들어지는 걸 처음 확실히 느꼈어요. 그때부터 일을 챙기고 정리정돈을 유지하는 게 더 어려워진 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이런 기억력 문제가 일상생활이나 업무에 어려움을 일으키고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 조금요. 그럭저럭 일상은 유지하고 있는데, 직장에서 사소한 후속 업무를 몇 번 놓쳤고 학교 마감도 몇 번 놓쳤어요. 이런 일이 꽤 생겨서 이러다 제가 못 미더운 사람처럼 보이지 않을까 걱정되기 시작했어요. 특히 나중에 사무관리자 자리로 옮기고 싶어서 더 그래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 15개월 전 처음 알아차리신 이후로 기억력 문제가 더 심해지고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 갑자기 더 심해졌다고는 말 못 하겠는데, 15개월 전쯤 저녁 자격증 과정을 시작한 이후로 눈에 띄게 관리하기가 힘들어졌어요. 그때부터 계속 좀 더 문제가 되고 있는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이런 기억력 문제를 알아차리기 시작한 이후로 새로운 것을 배우는 데 어려움이 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 새로운 걸 배우는 건 되는데, 독서나 계획이 많이 필요한 일을 시작하는 게 힘들어요. 예를 들어 읽어야 할 챕터가 길거나 계획을 짜야 하면, 늦을 때까지 미루다가 퇴근 후에 급하게 몰아서 하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 집중하거나 주의를 기울이는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 있어요. 회사에서든 수업에서든, 전화벨이 울리거나 근처에서 사람들이 얘기하거나, 아니면 그냥 갑자기 집에서 해야 할 일이 생각나기만 해도 금방 흐트러져요. 그러면 제가 하던 일에 더 이상 집중하고 있지 않다는 걸 깨달아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 날짜나 시간, 혹은 본인이 있는 장소를 헷갈리신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 아니요, 딱히 없어요. 제가 어디 있는지, 오늘이 무슨 요일인지는 알아요. 바쁠 때 시간 가는 걸 놓칠 수는 있지만, 날짜나 장소에 대해 헷갈리지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 뭔가를 표현하려고 할 때 적절한 단어를 찾는 데 어려움을 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 딱히 없어요. 가끔 어떻게 말할지 생각하느라 잠깐 멈추긴 하는데, 단어를 찾는 데 진짜 문제가 있다고 느낀 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 결정을 내리는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 가끔은요, 네. 아무것도 결정을 못 하는 건 아닌데, 뭘 먼저 해야 할지 정하는 데서 막혀요. 회사에서는 보통 그럭저럭 따라가는데, 저녁 수업을 시작한 이후로는 제 책상이랑 수업 폴더, 이메일 알림들이 자꾸 쌓여서, 그냥 시작하는 대신 그걸 정리하느라 시간을 낭비하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 본인이 있는 곳이나 주변 상황에 대해 방향감각을 잃거나 혼란스럽게 느낀 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 제가 어디 있는지나 주변 상황이 헷갈린 적은 없어요. 가끔 산만해지긴 하는데, 방향감각을 잃은 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 일상 업무와 활동을 계획하고 정리하는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네, 조금요. 회사에서는 보통 그럭저럭 관리하는데, 저녁 수업을 시작한 이후로는 더 힘들어졌어요. 제 책상이랑 수업 폴더, 이메일 알림들이 다 쌓여서, 그냥 바로 시작하는 대신 뭘 먼저 해야 할지 파악하느라 너무 많은 시간을 쓰게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 요즘 대부분의 시간 동안 슬프거나 기분이 가라앉는다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 딱히 그런 건 아니에요. 가끔 답답하거나 벅차다고 느끼긴 하는데, 요즘 대부분의 시간 동안 슬프거나 기분이 가라앉았다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 어떤 날은 다른 날보다 생각이나 기억력이 더 또렷하다고 느끼는 날이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 어떤 날은 확실히 다른 날보다 나은 것 같긴 한데, 제가 더 많이 느끼는 건 건망증이에요. 평소에 잘 처리하던 사소한 것들을 계속 놓쳐요. 전화 회신을 깜빡하거나, 등록 서류 제출을 놓치거나, 퇴근길에 심부름 들르는 걸 잊거나 하는 식으로요. 그게 정말 제가 도움을 요청하게 된 이유예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 요즘 평소보다 더 피곤하다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 평소보다 더 피곤하다고 딱히 느낀 적은 없어요. 그러니까, 누구나처럼 지치긴 하는데, 눈에 띄게 큰 변화라고 할 만한 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 예전에 배웠던 것들을 기억하는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 그런 것 같지 않아요, 딱히요. 예전에 배웠던 걸 기억하는 데 문제가 있다고 느낀 적은 없어요. 그러니까... 오래된 정보를 말씀하시는 거라면, 그건 괜찮은 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 어떤 일이나 프로젝트를 위해 예전에 배운 정보를 필요할 때 떠올리는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 그게 큰 문제라고 딱히 느낀 적은 없어요, 적어도 명확하게는요. 예전에 뭔가 배운 게 있으면 필요할 때 보통 떠올릴 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 나중에 하려고 계획했던 일을 자주 깜빡하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 네, 실제로 그런 일이 있었어요. 나중에 뭔가 하려고 계획했는데, 그게 그냥 머릿속에서 사라져요. 전화 회신하기, 서류 제출하기, 퇴근길에 심부름 들르기 같은 거요. 다 사소한 것들인데, 그게 쌓여서 누군가에게 물어봐야겠다는 생각이 들 정도가 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 특정 시간에 하려고 계획했던 일을 자주 깜빡하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네. 보통 사소한 것들인데, 특정 시간에 뭔가 하려고 계획해 놓고 그냥 잊어버려요. 전화 회신하기, 등록 서류 제출하기, 퇴근길에 심부름 들르기 같은 거요. 그게 결국 제가 도움을 요청하게 만든 이유예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 약속이나 할 일처럼 나중에 하려고 계획했던 일들을 자주 깜빡하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 네, 그래요. 말씀드렸듯이, 주로 일상적인 사소한 것들이에요. 전화 회신하기, 등록 서류 제출하기, 퇴근길에 심부름 들르는 걸 기억하기 같은 거요. 보통 제가 잘 처리하던 일들인데, 요즘은 하려고 마음먹어도 그냥 잊어버려요. 그게 도움을 요청하기로 결심하게 된 이유예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 과거에 본인에게 있었던 일들을 기억하는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 전반적으로 과거의 일들을 기억하는 데 문제가 있다고는 생각하지 않아요. 그보다는 나중에 하려고 했던 일을 잊어버리는 쪽에 가까워요. 이미 저한테 일어났던 일들은... 그건 문제가 있다고 느낀 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)
 인구통계: 성별 여성 / 나이 36 / 직업상태 secretary or administrative assistant / 최종학력 고등학교 졸업
@@ -573,497 +997,41 @@
 증상 지속 기간: 1 year and 3 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S009
-배경 서술: 데보라는 정규직 비서 업무를 계속하면서 사무관리자 자리로 나아가기 위해 저녁 행정관리 자격증 과정에 등록했다. 이후 15개월 동안, 학업과 업무를 병행하는 부담이 그동안 그녀를 지탱해 주던 루틴들에 무리를 주었다. 그녀는 수업 자료와 사무 업무를 정리하는 데 어려움을 겪었고, 지속적인 노력이 필요한 읽기나 과제를 미루었으며, 다이어리와 USB 메모리를 자주 잃어버렸고, 강의실 소음이나 사무실 방해, 관련 없는 생각들 때문에 산만해졌다. 그녀는 대체로 신뢰할 만한 사람으로 남아 있었지만, 사소한 약속이나 등록 절차, 집안 심부름을 잊어버리기 시작했고, 같은 반 학생들은 그녀가 긴 수업 시간 동안 안절부절못하거나 중간에 자리를 뜨는 모습을 알아차렸다. 한 과정 지도교수가 주의력과 학습 관리 어려움에 대해 도움을 받아보라고 권유한 후, 데보라는 주치의에게 정신과 진료 의뢰를 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 평소에 잘 챙기던 사소한 일들을 자꾸 잊어버려서 오게 됐어요. 예를 들면 전화 회신을 깜빡하거나, 등록 서류 제출을 놓치거나, 퇴근길에 들르려고 했던 심부름을 완전히 잊어버리는 식으로요. 이런 일이 꽤 자주 생겨서 도움을 받아야겠다고 생각했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 기억력 문제를 언제 처음 알아차리셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 저녁 자격증 과정을 시작했던 15개월 전쯤부터 관리하기가 힘들어지는 걸 처음 확실히 느꼈어요. 그때부터 일을 챙기고 정리정돈을 유지하는 게 더 어려워진 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이런 기억력 문제가 일상생활이나 업무에 어려움을 일으키고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 조금요. 그럭저럭 일상은 유지하고 있는데, 직장에서 사소한 후속 업무를 몇 번 놓쳤고 학교 마감도 몇 번 놓쳤어요. 이런 일이 꽤 생겨서 이러다 제가 못 미더운 사람처럼 보이지 않을까 걱정되기 시작했어요. 특히 나중에 사무관리자 자리로 옮기고 싶어서 더 그래요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 15개월 전 처음 알아차리신 이후로 기억력 문제가 더 심해지고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 갑자기 더 심해졌다고는 말 못 하겠는데, 15개월 전쯤 저녁 자격증 과정을 시작한 이후로 눈에 띄게 관리하기가 힘들어졌어요. 그때부터 계속 좀 더 문제가 되고 있는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이런 기억력 문제를 알아차리기 시작한 이후로 새로운 것을 배우는 데 어려움이 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 새로운 걸 배우는 건 되는데, 독서나 계획이 많이 필요한 일을 시작하는 게 힘들어요. 예를 들어 읽어야 할 챕터가 길거나 계획을 짜야 하면, 늦을 때까지 미루다가 퇴근 후에 급하게 몰아서 하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 집중하거나 주의를 기울이는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 있어요. 회사에서든 수업에서든, 전화벨이 울리거나 근처에서 사람들이 얘기하거나, 아니면 그냥 갑자기 집에서 해야 할 일이 생각나기만 해도 금방 흐트러져요. 그러면 제가 하던 일에 더 이상 집중하고 있지 않다는 걸 깨달아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 날짜나 시간, 혹은 본인이 있는 장소를 헷갈리신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 아니요, 딱히 없어요. 제가 어디 있는지, 오늘이 무슨 요일인지는 알아요. 바쁠 때 시간 가는 걸 놓칠 수는 있지만, 날짜나 장소에 대해 헷갈리지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 뭔가를 표현하려고 할 때 적절한 단어를 찾는 데 어려움을 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 딱히 없어요. 가끔 어떻게 말할지 생각하느라 잠깐 멈추긴 하는데, 단어를 찾는 데 진짜 문제가 있다고 느낀 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 결정을 내리는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 가끔은요, 네. 아무것도 결정을 못 하는 건 아닌데, 뭘 먼저 해야 할지 정하는 데서 막혀요. 회사에서는 보통 그럭저럭 따라가는데, 저녁 수업을 시작한 이후로는 제 책상이랑 수업 폴더, 이메일 알림들이 자꾸 쌓여서, 그냥 시작하는 대신 그걸 정리하느라 시간을 낭비하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 본인이 있는 곳이나 주변 상황에 대해 방향감각을 잃거나 혼란스럽게 느낀 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 제가 어디 있는지나 주변 상황이 헷갈린 적은 없어요. 가끔 산만해지긴 하는데, 방향감각을 잃은 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 일상 업무와 활동을 계획하고 정리하는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네, 조금요. 회사에서는 보통 그럭저럭 관리하는데, 저녁 수업을 시작한 이후로는 더 힘들어졌어요. 제 책상이랑 수업 폴더, 이메일 알림들이 다 쌓여서, 그냥 바로 시작하는 대신 뭘 먼저 해야 할지 파악하느라 너무 많은 시간을 쓰게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 요즘 대부분의 시간 동안 슬프거나 기분이 가라앉는다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 딱히 그런 건 아니에요. 가끔 답답하거나 벅차다고 느끼긴 하는데, 요즘 대부분의 시간 동안 슬프거나 기분이 가라앉았다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 어떤 날은 다른 날보다 생각이나 기억력이 더 또렷하다고 느끼는 날이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 어떤 날은 확실히 다른 날보다 나은 것 같긴 한데, 제가 더 많이 느끼는 건 건망증이에요. 평소에 잘 처리하던 사소한 것들을 계속 놓쳐요. 전화 회신을 깜빡하거나, 등록 서류 제출을 놓치거나, 퇴근길에 심부름 들르는 걸 잊거나 하는 식으로요. 그게 정말 제가 도움을 요청하게 된 이유예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 요즘 평소보다 더 피곤하다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 평소보다 더 피곤하다고 딱히 느낀 적은 없어요. 그러니까, 누구나처럼 지치긴 하는데, 눈에 띄게 큰 변화라고 할 만한 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 예전에 배웠던 것들을 기억하는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 그런 것 같지 않아요, 딱히요. 예전에 배웠던 걸 기억하는 데 문제가 있다고 느낀 적은 없어요. 그러니까... 오래된 정보를 말씀하시는 거라면, 그건 괜찮은 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 어떤 일이나 프로젝트를 위해 예전에 배운 정보를 필요할 때 떠올리는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 그게 큰 문제라고 딱히 느낀 적은 없어요, 적어도 명확하게는요. 예전에 뭔가 배운 게 있으면 필요할 때 보통 떠올릴 수 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 나중에 하려고 계획했던 일을 자주 깜빡하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 네, 실제로 그런 일이 있었어요. 나중에 뭔가 하려고 계획했는데, 그게 그냥 머릿속에서 사라져요. 전화 회신하기, 서류 제출하기, 퇴근길에 심부름 들르기 같은 거요. 다 사소한 것들인데, 그게 쌓여서 누군가에게 물어봐야겠다는 생각이 들 정도가 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 특정 시간에 하려고 계획했던 일을 자주 깜빡하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네. 보통 사소한 것들인데, 특정 시간에 뭔가 하려고 계획해 놓고 그냥 잊어버려요. 전화 회신하기, 등록 서류 제출하기, 퇴근길에 심부름 들르기 같은 거요. 그게 결국 제가 도움을 요청하게 만든 이유예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 약속이나 할 일처럼 나중에 하려고 계획했던 일들을 자주 깜빡하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 네, 그래요. 말씀드렸듯이, 주로 일상적인 사소한 것들이에요. 전화 회신하기, 등록 서류 제출하기, 퇴근길에 심부름 들르는 걸 기억하기 같은 거요. 보통 제가 잘 처리하던 일들인데, 요즘은 하려고 마음먹어도 그냥 잊어버려요. 그게 도움을 요청하기로 결심하게 된 이유예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 과거에 본인에게 있었던 일들을 기억하는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 전반적으로 과거의 일들을 기억하는 데 문제가 있다고는 생각하지 않아요. 그보다는 나중에 하려고 했던 일을 잊어버리는 쪽에 가까워요. 이미 저한테 일어났던 일들은... 그건 문제가 있다고 느낀 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 데보라는 정규직 비서 업무를 계속하면서 사무관리자 자리로 나아가기 위해 저녁 행정관리 자격증 과정에 등록했다. 이후 15개월 동안, 학업과 업무를 병행하는 부담이 그동안 그녀를 지탱해 주던 루틴들에 무리를 주었다. 그녀는 수업 자료와 사무 업무를 정리하는 데 어려움을 겪었고, 지속적인 노력이 필요한 읽기나 과제를 미루었으며, 다이어리와 USB 메모리를 자주 잃어버렸고, 강의실 소음이나 사무실 방해, 관련 없는 생각들 때문에 산만해졌다. 그녀는 대체로 신뢰할 만한 사람으로 남아 있었지만, 사소한 약속이나 등록 절차, 집안 심부름을 잊어버리기 시작했고, 같은 반 학생들은 그녀가 긴 수업 시간 동안 안절부절못하거나 중간에 자리를 뜨는 모습을 알아차렸다. 한 과정 지도교수가 주의력과 학습 관리 어려움에 대해 도움을 받아보라고 권유한 후, 데보라는 주치의에게 정신과 진료 의뢰를 요청했다.
+표집된 증상 목록:
+  - S005 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+  - S006 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.
+  - S007 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.
+  - S008 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).
+  - S009 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
+  - S010 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.
+  - S011 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: R41.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
-  누락: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: None (None, ICD: R41.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 없음
+체크리스트 그룹: inattention (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.
+  - 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.
+  - 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).
+  - 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).
+체크리스트 그룹: hyperactivity_impulsivity (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S004_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S004_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -983,6 +983,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1027,11 +1032,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D002_S004_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D002_S004_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -553,6 +554,7 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
